--- a/influencer_forms/005_influencer_campaign_quote_request--influencer_forms.xlsx
+++ b/influencer_forms/005_influencer_campaign_quote_request--influencer_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>brand_info</t>
+          <t>brand_info_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brand Name</t>
+          <t>Brand Info 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>budget_rate_card</t>
+          <t>budget_rate_card_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Rate Card</t>
+          <t>Budget Rate Card 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>budget_note</t>
+          <t>budget_note_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Budget Note 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Location</t>
+          <t>Target Audience Location</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>target_audience_gender</t>
+          <t>target_audience_gender_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Gender</t>
+          <t>Target Audience Gender 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1432,7 +1432,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>target_audience_gender_choices</t>
+          <t>target_audience_gender_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1449,7 +1449,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>target_audience_gender_choices</t>
+          <t>target_audience_gender_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1466,7 +1466,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>target_audience_gender_choices</t>
+          <t>target_audience_gender_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
